--- a/processed_ruby_restored_xlsx/sc215_ノノ７：尿検査.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc215_ノノ７：尿検査.ss.xlsx
@@ -515,8 +515,8 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>What was it…? I feel like I can remember it and I feel
-like I can't… hmm…</t>
+          <t>What was it…? I feel like I can remember it and I
+feel like I can't… hmm…</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1587,8 +1587,8 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>「Ehh... ahem！ Memory's a fuzzy thing. Even things from
-ten minutes ago can get forgotten.」</t>
+          <t>「Ehh... ahem！ Memory's a fuzzy thing. Even things
+from ten minutes ago can get forgotten.」</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1710,9 +1710,9 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>「I-mean！ If it's important, something will trigger the
-memory and it'll pop back up, so let's focus on the
-task for now~！」</t>
+          <t>「I-mean！ If it's important, something will trigger
+the memory and it'll pop back up, so let's focus on
+the task for now~！」</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1772,8 +1772,8 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>With that in mind, I stopped thinking and went back to
-work.</t>
+          <t>With that in mind, I stopped thinking and went back
+to work.</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1803,8 +1803,8 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>「Okay, I'll tidy up here, so Janitor-sensei, could you
-take care of that over there！」</t>
+          <t>「Okay, I'll tidy up here, so Janitor-sensei, could
+you take care of that over there！」</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1849,8 +1849,8 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>Also, watching Nono-chan get so proud makes me want to
-go along with her.</t>
+          <t>Also, watching Nono-chan get so proud makes me want
+to go along with her.</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1955,8 +1955,8 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>As I reached to hand the fallen printout to Nono-chan,
-I happened to glance at the writing on it.</t>
+          <t>As I reached to hand the fallen printout to
+Nono-chan, I happened to glance at the writing on it.</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2077,8 +2077,8 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan-sensei asks, delighted as if it were her own
-good news.</t>
+          <t>Nono-chan-sensei asks, delighted as if it were her
+own good news.</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2338,8 +2338,8 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>Apparently she really had misunderstood, not trying to
-cover it up.</t>
+          <t>Apparently she really had misunderstood, not trying
+to cover it up.</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2385,7 +2385,8 @@
       <c r="B126" s="1" t="inlineStr">
         <is>
           <t>True to form, once she realizes it's a
-misunderstanding, Nono-chan suddenly starts panicking.</t>
+misunderstanding, Nono-chan suddenly starts
+panicking.</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2446,8 +2447,8 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>「Wah！ Y-you don't have to say the rest, I know what to
-do！」</t>
+          <t>「Wah！ Y-you don't have to say the rest, I know what
+to do！」</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2708,8 +2709,8 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>…If that's the case, I've got to do something about it
-for you！</t>
+          <t>…If that's the case, I've got to do something about
+it for you！</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2907,8 +2908,8 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan narrows her eyes while still staring fixedly
-at my face.</t>
+          <t>Nono-chan narrows her eyes while still staring
+fixedly at my face.</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -3121,8 +3122,8 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>「That's not okay！ You might catch a nasty illness, you
-know？」</t>
+          <t>「That's not okay！ You might catch a nasty illness,
+you know？」</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3365,8 +3366,8 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>When I glanced over, Nono-chan was shyly fidgeting and
-wriggling her legs.</t>
+          <t>When I glanced over, Nono-chan was shyly fidgeting
+and wriggling her legs.</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3472,8 +3473,9 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>I stand up, fired up, and swiftly scoop up Nono-chan's
-tiny body, carrying her in a princess carry.</t>
+          <t>I stand up, fired up, and swiftly scoop up
+Nono-chan's tiny body, carrying her in a princess
+carry.</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3563,8 +3565,8 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>「Wait！ Janitor-sensei！？ A-aren't you getting the wrong
-idea~？」</t>
+          <t>「Wait！ Janitor-sensei！？ A-aren't you getting the
+wrong idea~？」</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3640,8 +3642,8 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>It was forceful, but what’s done is done — my body had
-already moved.</t>
+          <t>It was forceful, but what’s done is done — my body
+had already moved.</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3985,8 +3987,8 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>…We definitely got carried away with the momentum, and
-it's turned into a pretty intense mess.</t>
+          <t>…We definitely got carried away with the momentum,
+and it's turned into a pretty intense mess.</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -4091,8 +4093,8 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>Upon hearing that Nono-chan couldn't pee, I offered to
-help.</t>
+          <t>Upon hearing that Nono-chan couldn't pee, I offered
+to help.</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4533,8 +4535,8 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t>I try pressing my belly, and a sound immediately slips
-out.</t>
+          <t>I try pressing my belly, and a sound immediately
+slips out.</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4689,8 +4691,8 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>When I pressed her lower belly, Nono-chan's small body
-gave a little shudder.</t>
+          <t>When I pressed her lower belly, Nono-chan's small
+body gave a little shudder.</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4705,7 +4707,8 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>Seeing that adorable reaction made me want to be mean.</t>
+          <t>Seeing that adorable reaction made me want to be
+mean.</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -5869,8 +5872,8 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t>She couldn't say anything—maybe she was waiting for me
-to speak.</t>
+          <t>She couldn't say anything—maybe she was waiting for
+me to speak.</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -5994,8 +5997,8 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>「Aah... I’m so embarrassed... it’s too embarrassing...
-I feel like I might just lose it...」</t>
+          <t>「Aah... I’m so embarrassed... it’s too
+embarrassing... I feel like I might just lose it...」</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -6026,8 +6029,8 @@
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t>But seeing her fidgeting her legs like that, she might
-be about to lose the ability to hold her pee.</t>
+          <t>But seeing her fidgeting her legs like that, she
+might be about to lose the ability to hold her pee.</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -6149,8 +6152,8 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t>I lowered my voice and murmured once more right by her
-ear.</t>
+          <t>I lowered my voice and murmured once more right by
+her ear.</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -6240,8 +6243,8 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t>「Ugh—！ That's not it... fua, hah！ You have to properly
-collect the urine... fuaah！」</t>
+          <t>「Ugh—！ That's not it... fua, hah！ You have to
+properly collect the urine... fuaah！」</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -6347,8 +6350,8 @@
       </c>
       <c r="B384" s="1" t="inlineStr">
         <is>
-          <t>Along with that, she keeps squeezing her eyes shut and
-lifting her shoulders.</t>
+          <t>Along with that, she keeps squeezing her eyes shut
+and lifting her shoulders.</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -6682,8 +6685,8 @@
       </c>
       <c r="B406" s="1" t="inlineStr">
         <is>
-          <t>Though I said I'd put it in, I actually held back from
-inserting it and squeezed down hard.</t>
+          <t>Though I said I'd put it in, I actually held back
+from inserting it and squeezed down hard.</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -7049,7 +7052,8 @@
       </c>
       <c r="B430" s="1" t="inlineStr">
         <is>
-          <t>My words are still stiff, but my body honestly reacts.</t>
+          <t>My words are still stiff, but my body honestly
+reacts.</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -7095,8 +7099,8 @@
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t>「…Okay, I'm going to start moving, so if you feel like
-you need to pee, tell me, okay？」</t>
+          <t>「…Okay, I'm going to start moving, so if you feel
+like you need to pee, tell me, okay？」</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -7157,8 +7161,8 @@
       </c>
       <c r="B437" s="1" t="inlineStr">
         <is>
-          <t>Her pussy wraps around my fingers, and a naughty juice
-drips out from between her legs…</t>
+          <t>Her pussy wraps around my fingers, and a naughty
+juice drips out from between her legs…</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -7233,8 +7237,8 @@
       </c>
       <c r="B442" s="1" t="inlineStr">
         <is>
-          <t>Even though I wasn't moving the finger I had inserted,
-her voice was already melting away.</t>
+          <t>Even though I wasn't moving the finger I had
+inserted, her voice was already melting away.</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -7495,8 +7499,8 @@
       <c r="B459" s="1" t="inlineStr">
         <is>
           <t>Rubbing slowly as if savoring her very sensitive
-vaginal walls, Nono-chan begins to let out rather loud
-sounds.</t>
+vaginal walls, Nono-chan begins to let out rather
+loud sounds.</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7650,9 +7654,9 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>My body yields to the pleasure, my juices keep welling
-up, and it feels like even my fingers are going to be
-melted into goo….</t>
+          <t>My body yields to the pleasure, my juices keep
+welling up, and it feels like even my fingers are
+going to be melted into goo….</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -8021,8 +8025,8 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t>As Nono-chan's hips buck upward, I move my hand up and
-down, matching her rhythm.</t>
+          <t>As Nono-chan's hips buck upward, I move my hand up
+and down, matching her rhythm.</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -8069,7 +8073,8 @@
       </c>
       <c r="B496" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chan, you're making such a sexy face, you know？」</t>
+          <t>「Nono-chan, you're making such a sexy face, you
+know？」</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -8561,8 +8566,8 @@
       </c>
       <c r="B528" s="1" t="inlineStr">
         <is>
-          <t>「U-aaa... hah, haaah! Aaaah, nnh! It— it's coming out,
-aaahhh, nngaaahh!」</t>
+          <t>「U-aaa... hah, haaah! Aaaah, nnh! It— it's coming
+out, aaahhh, nngaaahh!」</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -8592,8 +8597,8 @@
       </c>
       <c r="B530" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan's tiny body jolted upward with a big, sudden
-bounce.</t>
+          <t>Nono-chan's tiny body jolted upward with a big,
+sudden bounce.</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -8732,8 +8737,8 @@
       </c>
       <c r="B539" s="1" t="inlineStr">
         <is>
-          <t>Her knees gave out and Nono-chan let out a weak little
-sound.</t>
+          <t>Her knees gave out and Nono-chan let out a weak
+little sound.</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -8748,8 +8753,8 @@
       </c>
       <c r="B540" s="1" t="inlineStr">
         <is>
-          <t>Almost at the same time, the leaking urine spurted out
-in an arc.</t>
+          <t>Almost at the same time, the leaking urine spurted
+out in an arc.</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -8854,8 +8859,8 @@
       </c>
       <c r="B547" s="1" t="inlineStr">
         <is>
-          <t>I was so transfixed by the unending stream of pee that
-I even forgot to collect it.</t>
+          <t>I was so transfixed by the unending stream of pee
+that I even forgot to collect it.</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -8931,7 +8936,8 @@
       </c>
       <c r="B552" s="1" t="inlineStr">
         <is>
-          <t>「Haa... hafuu...！ Nngh... D-did I pee... come out...？」</t>
+          <t>「Haa... hafuu...！ Nngh... D-did I pee... come
+out...？」</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -9053,7 +9059,8 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... niyo— the examination... what should I do...？」</t>
+          <t>「Ugh... niyo— the examination... what should I
+do...？」</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9084,9 +9091,9 @@
       </c>
       <c r="B562" s="1" t="inlineStr">
         <is>
-          <t>Your fingers were squeezing me so tightly like that...
-if you put your penis in, it would probably feel even
-better.</t>
+          <t>Your fingers were squeezing me so tightly like
+that... if you put your penis in, it would probably
+feel even better.</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -9209,8 +9216,8 @@
       </c>
       <c r="B570" s="1" t="inlineStr">
         <is>
-          <t>Saying that, I yanked down what she was wearing all at
-once and exposed my penis.</t>
+          <t>Saying that, I yanked down what she was wearing all
+at once and exposed my penis.</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -9928,7 +9935,8 @@
       </c>
       <c r="B617" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ha！ Yes… nnaaa！ I'm c-coming… ple-ase, nna！ Ahh！」</t>
+          <t>「Ah, ha！ Yes… nnaaa！ I'm c-coming… ple-ase, nna！
+Ahh！」</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -10174,8 +10182,8 @@
       </c>
       <c r="B633" s="1" t="inlineStr">
         <is>
-          <t>「Haaa, hah！ Yes！ I... it feels good, it feels... good！
-It feels so good！」</t>
+          <t>「Haaa, hah！ Yes！ I... it feels good, it feels...
+good！ It feels so good！」</t>
         </is>
       </c>
       <c r="C633" t="n">
@@ -10527,7 +10535,8 @@
       </c>
       <c r="B656" s="1" t="inlineStr">
         <is>
-          <t>「Hah, ha！ Heh… aaah！ Mui-sensei's penis is… so lewd…！」</t>
+          <t>「Hah, ha！ Heh… aaah！ Mui-sensei's penis is… so
+lewd…！」</t>
         </is>
       </c>
       <c r="C656" t="n">
@@ -10681,8 +10690,8 @@
       </c>
       <c r="B666" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ha, ah！  So happy... ugh...！  Mmm, nfu, fuh！  Nn,
-nn...！」</t>
+          <t>「Ah, ha, ah！  So happy... ugh...！  Mmm, nfu, fuh！
+Nn, nn...！」</t>
         </is>
       </c>
       <c r="C666" t="n">
@@ -10713,8 +10722,8 @@
       </c>
       <c r="B668" s="1" t="inlineStr">
         <is>
-          <t>A numbness starts from my waist and shoots straight up
-through my skull… the kind of languor that pierces
+          <t>A numbness starts from my waist and shoots straight
+up through my skull… the kind of languor that pierces
 through you.</t>
         </is>
       </c>
@@ -11544,8 +11553,8 @@
       </c>
       <c r="B722" s="1" t="inlineStr">
         <is>
-          <t>...Nono-chan trembles with her sweaty body, continuing
-to pant heavily.</t>
+          <t>...Nono-chan trembles with her sweaty body,
+continuing to pant heavily.</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -11868,8 +11877,8 @@
       </c>
       <c r="B743" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan lets out a cry that's as if she's surprised,
-and yet utterly adorable.</t>
+          <t>Nono-chan lets out a cry that's as if she's
+surprised, and yet utterly adorable.</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -12192,7 +12201,8 @@
       </c>
       <c r="B764" s="1" t="inlineStr">
         <is>
-          <t>I just felt deflated and kept nodding like an idiot...</t>
+          <t>I just felt deflated and kept nodding like an
+idiot...</t>
         </is>
       </c>
       <c r="C764" t="n">
@@ -12407,8 +12417,8 @@
       </c>
       <c r="B778" s="1" t="inlineStr">
         <is>
-          <t>「Wah！ N-no, that's not...！ It's just... you know！ Like
-the flow and stuff...！ I just...！」</t>
+          <t>「Wah！ N-no, that's not...！ It's just... you know！
+Like the flow and stuff...！ I just...！」</t>
         </is>
       </c>
       <c r="C778" t="n">
@@ -12453,8 +12463,8 @@
       </c>
       <c r="B781" s="1" t="inlineStr">
         <is>
-          <t>I pretend not to notice, but even she can tell my face
-is grinning.</t>
+          <t>I pretend not to notice, but even she can tell my
+face is grinning.</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -12561,8 +12571,9 @@
       </c>
       <c r="B788" s="1" t="inlineStr">
         <is>
-          <t>When I said it after thinking about pee collection and
-sex at the same time, I ended up getting scolded...</t>
+          <t>When I said it after thinking about pee collection
+and sex at the same time, I ended up getting
+scolded...</t>
         </is>
       </c>
       <c r="C788" t="n">

--- a/processed_ruby_restored_xlsx/sc215_ノノ７：尿検査.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc215_ノノ７：尿検査.ss.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>…and then I spotted Nono-chan passing by.</t>
+          <t>…and then he spotted Nono-chan passing by.</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -576,8 +576,8 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Putting aside whatever it was I couldn't remember for
-the moment, I immediately called out.</t>
+          <t>Putting aside whatever it was he couldn't remember
+for the moment, he immediately called out.</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -607,7 +607,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Janitor-sensei！ W-w-wait...」</t>
+          <t>Ah... Janitor-sensei！ W-w-wait...</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -623,7 +623,7 @@
       <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Holding some documents, Nono-chan lost her balance as
-she turned toward my voice.</t>
+she turned toward his voice.</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -669,7 +669,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Saying that, I reached my hand under the papers.</t>
+          <t>Saying that, he reached his hand under the papers.</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>In case she dropped them, I made sure I could catch
+          <t>In case she dropped them, he made sure he could catch
 them right away.</t>
         </is>
       </c>
@@ -807,8 +807,8 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>「...Is that really okay？ Doesn't Janitor-sensei have
-work to do as well？」</t>
+          <t>...Is that really okay？ Doesn't Janitor-sensei have
+work to do as well？</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>So basically, it's best not to overthink it.'</t>
+          <t>So basically, it's best not to overthink it.」</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1803,8 +1803,8 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>「Okay, I'll tidy up here, so Janitor-sensei, could
-you take care of that over there！」</t>
+          <t>Okay, I'll tidy up here, so Janitor-sensei, could you
+take care of that over there！</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2508,8 +2508,8 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>And after putting the documents on the desk, she
-sprints straight to the bathroom.</t>
+          <t>And after putting the documents on the desk, they
+sprint straight to the bathroom.</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>「I-I couldn't do it...」</t>
+          <t>I-I couldn't do it...</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>「If possible... yeah.」</t>
+          <t>If possible... yeah.</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -3122,8 +3122,8 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>「That's not okay！ You might catch a nasty illness,
-you know？」</t>
+          <t>That's not okay！ You might catch a nasty illness, you
+know？</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>「Indeed... there are such cases, but...」</t>
+          <t>Indeed... there are such cases, but...</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3275,8 +3275,8 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>「Eh, um... um, Janitor-sensei...？ What do you mean by
-that...？」</t>
+          <t>Eh, um... um, Janitor-sensei...？ What do you mean by
+that...？</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>「Huh？ Could it be that you're about to come？」</t>
+          <t>Huh？ Could it be that you're about to come？</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3565,8 +3565,8 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>「Wait！ Janitor-sensei！？ A-aren't you getting the
-wrong idea~？」</t>
+          <t>Wait！ Janitor-sensei！？ A-aren't you getting the wrong
+idea~？</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t>「N-No, that's not true！」</t>
+          <t>N-No, that's not true！</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>「Hyah！」</t>
+          <t>Hyah！</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t>I try pressing my belly, and a sound immediately
+          <t>I try pressing his belly, and a sound immediately
 slips out.</t>
         </is>
       </c>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>When I pressed her lower belly, Nono-chan's small
+          <t>When he pressed her lower belly, Nono-chan's small
 body gave a little shudder.</t>
         </is>
       </c>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>Seeing that adorable reaction made me want to be
+          <t>Seeing that adorable reaction made him want to be
 mean.</t>
         </is>
       </c>
@@ -4921,7 +4921,8 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>So, I gently stroke her belly instead of her head.</t>
+          <t>So, I gently stroke their belly instead of their
+head.</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -5166,7 +5167,7 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>「Ah... nmm！ Janitor... se...nsei...」</t>
+          <t>Ah... nmm！ Janitor... se...nsei...</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5289,7 +5290,7 @@
       <c r="B315" s="1" t="inlineStr">
         <is>
           <t>Stressing all along that she's just helping with a
-urine test, I slide my finger toward Nono-chan's
+urine test, he slides his finger toward Nono-chan's
 crotch... the most important place.</t>
         </is>
       </c>
@@ -5396,8 +5397,8 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>「Fwaa... b-because... Janitor-sensei's hands are so
-lewd...」</t>
+          <t>Fwaa... b-because... Janitor-sensei's hands are so
+lewd...</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -5549,8 +5550,8 @@
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t>When I emphasized that it was just helping, Nono-chan
-reluctantly nodded.</t>
+          <t>When he emphasized that it was just helping,
+Nono-chan reluctantly nodded.</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5919,8 +5920,8 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t>「I-If I'm really going to be made to pee... I just
-don't even know how to put it into words...」</t>
+          <t>I-If I'm really going to be made to pee... I just
+don't even know how to put it into words...</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -5966,8 +5967,8 @@
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t>「Heh... having someone help you pee makes you sound
-like a baby, doesn't it?」</t>
+          <t>Heh... having someone help you pee makes you sound
+like a baby, doesn't it?</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -6029,8 +6030,8 @@
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t>But seeing her fidgeting her legs like that, she
-might be about to lose the ability to hold her pee.</t>
+          <t>But seeing them fidgeting their legs like that, they
+might be about to lose the ability to hold their pee.</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -7452,8 +7453,8 @@
       </c>
       <c r="B456" s="1" t="inlineStr">
         <is>
-          <t>「Alright then, I'll do my best to live up to your
-expectations, okay？」</t>
+          <t>Alright then, I'll do my best to live up to your
+expectations, okay？</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -7483,7 +7484,7 @@
       </c>
       <c r="B458" s="1" t="inlineStr">
         <is>
-          <t>「Yah！ Ah！ Hah...！ Nn, nnh！ Ah！ Ahh！ Aahh！」</t>
+          <t>Yah！ Ah！ Hah...！ Nn, nnh！ Ah！ Ahh！ Aahh！</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -7530,7 +7531,7 @@
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t>「I wonder if this feels good here？」</t>
+          <t>I wonder if this feels good here？</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -7732,8 +7733,8 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh, hah！ Aah！ Janitor-sensei！ So much！ If you do
-that to me—！」</t>
+          <t>Nnngh, hah！ Aah！ Janitor-sensei！ So much！ If you do
+that to me—！</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -8009,8 +8010,8 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>「Haa, ah！ It feels so good！ Nn！ Amazing！ Hah！ Yes,
-yes—it's good！」</t>
+          <t>Haa, ah！ It feels so good！ Nn！ Amazing！ Hah！ Yes,
+yes—it's good！</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8890,7 +8891,7 @@
       </c>
       <c r="B549" s="1" t="inlineStr">
         <is>
-          <t>「Haaah...！ Ah, haa, fuu... nnn, fuu... fwaaa...」</t>
+          <t>Haaah...！ Ah, haa, fuu... nnn, fuu... fwaaa...</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -8936,8 +8937,7 @@
       </c>
       <c r="B552" s="1" t="inlineStr">
         <is>
-          <t>「Haa... hafuu...！ Nngh... D-did I pee... come
-out...？」</t>
+          <t>Haa... hafuu...！ Nngh... D-did I pee... come out...？</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -9216,8 +9216,8 @@
       </c>
       <c r="B570" s="1" t="inlineStr">
         <is>
-          <t>Saying that, I yanked down what she was wearing all
-at once and exposed my penis.</t>
+          <t>Saying that, he yanked down what she was wearing all
+at once and exposed his penis.</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="B575" s="1" t="inlineStr">
         <is>
-          <t>My penis was completely hard, about to burst.</t>
+          <t>His penis was completely hard, about to burst.</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t>Then, blurting out my true feelings, I pressed my
+          <t>Then, blurting out his true feelings, he pressed his
 penis against her.</t>
         </is>
       </c>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="B644" s="1" t="inlineStr">
         <is>
-          <t>「Mmm！ Yooo, Mui-sensei…」</t>
+          <t>Mmm！ Yooo, Mui-sensei…</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="B646" s="1" t="inlineStr">
         <is>
-          <t>Each time Nono's hips collide with my body, a loud,
+          <t>Each time Nono's hips collide with his body, a loud,
 slapping sound rings out.</t>
         </is>
       </c>
@@ -10535,8 +10535,7 @@
       </c>
       <c r="B656" s="1" t="inlineStr">
         <is>
-          <t>「Hah, ha！ Heh… aaah！ Mui-sensei's penis is… so
-lewd…！」</t>
+          <t>Hah, ha！ Heh… aaah！ Mui-sensei's penis is… so lewd…！</t>
         </is>
       </c>
       <c r="C656" t="n">
@@ -10877,8 +10876,8 @@
       </c>
       <c r="B678" s="1" t="inlineStr">
         <is>
-          <t>「Haaah... Mui-sensei, b-because... you're making such
-an indecent face... desu...」</t>
+          <t>Haaah... Mui-sensei, b-because... you're making such
+an indecent face... desu...</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -11045,8 +11044,8 @@
       </c>
       <c r="B689" s="1" t="inlineStr">
         <is>
-          <t>So lost in it I keep thrusting my hips, like even
-breathing would be a waste.</t>
+          <t>So lost in it they keep thrusting their hips, like
+even breathing would be a waste.</t>
         </is>
       </c>
       <c r="C689" t="n">
@@ -11061,7 +11060,8 @@
       </c>
       <c r="B690" s="1" t="inlineStr">
         <is>
-          <t>I pound into her, devouring this pleasurable feeling.</t>
+          <t>They pound into me, devouring this pleasurable
+feeling.</t>
         </is>
       </c>
       <c r="C690" t="n">
@@ -11277,8 +11277,8 @@
       </c>
       <c r="B704" s="1" t="inlineStr">
         <is>
-          <t>「Hey, mui-sensei！ Together... together with me！ Ah,
-aaahhh, nngh！」</t>
+          <t>Hey, mui-sensei！ Together... together with me！ Ah,
+aaahhh, nngh！</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -11445,8 +11445,8 @@
       </c>
       <c r="B715" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaaa...！ Ha, ha！ Yoo, Mui-sensee... nn, fuuuh,
-mmm！？」</t>
+          <t>Fuwaaa...！ Ha, ha！ Yoo, Mui-sensee... nn, fuuuh,
+mmm！？</t>
         </is>
       </c>
       <c r="C715" t="n">
@@ -11461,8 +11461,8 @@
       </c>
       <c r="B716" s="1" t="inlineStr">
         <is>
-          <t>While I'm ejaculating, I can feel Nono-chan's climax,
-and the pleasure won't stop...！</t>
+          <t>While I'm ejaculating, I can feel Monono-chan's
+climax, and the pleasure won't stop...！</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="B740" s="1" t="inlineStr">
         <is>
-          <t>At the same time my penis jolted up and, with force,
+          <t>At the same time his penis jolted up and, with force,
 shot out of her vagina.</t>
         </is>
       </c>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="B763" s="1" t="inlineStr">
         <is>
-          <t>「Ah... yeah, I guess so...」</t>
+          <t>Ah... yeah, I guess so...</t>
         </is>
       </c>
       <c r="C763" t="n">
